--- a/app1/Excelfiles/test2.xlsx
+++ b/app1/Excelfiles/test2.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -850,13 +850,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/app1/Excelfiles/test2.xlsx
+++ b/app1/Excelfiles/test2.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -855,13 +855,28 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
